--- a/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
+++ b/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
@@ -70,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -92,11 +92,55 @@
         <color rgb="00BBBBBB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +170,8 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,11 +571,11 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Superficie cubierta que se vende (ficha)</t>
+          <t>Superficie cubierta (presupuesto SIPCOR #2790, 08/09/26)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -730,8 +776,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -769,7 +813,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -915,7 +958,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
@@ -937,6 +979,10 @@
           <t>Está en el Excel de materiales ($850.000 + $3.240.000) y la planilla de mano de obra también tiene días de instalaciones. Puede estar contada dos veces (≈ USD 2.640).</t>
         </is>
       </c>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="22" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -949,9 +995,13 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>El Excel de costos divide por 78 m²; la ficha vende 72 m², la planilla de mano de obra usa 72 y el presupuesto SIPCOR dice 73 m². Con 72 m² el costo por m² sube un 8%.</t>
-        </is>
-      </c>
+          <t>Definido: 73 m² cubiertos (presupuesto SIPCOR #2790). El Excel de costos usaba 78 m² y la ficha y la planilla de mano de obra, 72 m². Hay que corregir la ficha.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="22" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -967,6 +1017,10 @@
           <t>La ficha dice cubierta SIP EPS 50 mm; el Excel cotiza cabios de pino + chapa. Confirmar que los paneles de techo están dentro del kit de $26,9 M.</t>
         </is>
       </c>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1281,7 +1335,6 @@
       </c>
       <c r="E13" s="20" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="D15" s="8" t="inlineStr">
         <is>
@@ -1320,7 +1373,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -1519,7 +1571,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>

--- a/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
+++ b/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,6 +172,13 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -595,7 +602,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>Errores!F7</f>
+        <f>Errores!F8</f>
         <v/>
       </c>
     </row>
@@ -794,7 +801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -944,58 +951,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="E7" s="8" t="inlineStr">
+      <c r="A7" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Kit de paneles SIPCOR</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>$26.928.565 = USD 17.600,37 al dólar $1.530 (7/9)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>USD 17.600,37 al dólar del costo ($1.550) = $27.280.574</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>26928565.49</v>
+      </c>
+      <c r="F7" s="24">
+        <f>E7-17600.37*Resumen!B3</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>F7/Resumen!$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F7" s="19">
-        <f>SUM(F4:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="9">
-        <f>F7/Resumen!B3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="F8" s="19">
+        <f>SUM(F4:F7)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>F8/Resumen!B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>A verificar (no se descontó):</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Mano de obra sanitaria y eléctrica</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Está en el Excel de materiales ($850.000 + $3.240.000) y la planilla de mano de obra también tiene días de instalaciones. Puede estar contada dos veces (≈ USD 2.640).</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Superficie</t>
+          <t>Mano de obra sanitaria y eléctrica</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Definido: 73 m² cubiertos (presupuesto SIPCOR #2790). El Excel de costos usaba 78 m² y la ficha y la planilla de mano de obra, 72 m². Hay que corregir la ficha.</t>
+          <t>Está en el Excel de materiales ($850.000 + $3.240.000) y la planilla de mano de obra también tiene días de instalaciones. Puede estar contada dos veces (≈ USD 2.640).</t>
         </is>
       </c>
       <c r="D11" s="21" t="n"/>
@@ -1003,18 +1022,18 @@
       <c r="F11" s="21" t="n"/>
       <c r="G11" s="22" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cubierta</t>
+          <t>Superficie</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>La ficha dice cubierta SIP EPS 50 mm; el Excel cotiza cabios de pino + chapa. Confirmar que los paneles de techo están dentro del kit de $26,9 M.</t>
+          <t>Definido: 73 m² cubiertos (presupuesto SIPCOR #2790). El Excel de costos usaba 78 m² y la ficha y la planilla de mano de obra, 72 m². Hay que corregir la ficha.</t>
         </is>
       </c>
       <c r="D12" s="21" t="n"/>
@@ -1022,9 +1041,44 @@
       <c r="F12" s="21" t="n"/>
       <c r="G12" s="22" t="n"/>
     </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Cubierta</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Definido por Adrián: paneles SIP 50 de techo (incluidos en el kit SIPCOR: 55 paneles MDF ranurado, con membrana hidrófuga y Easy Band) + cabios de madera + alfajías + clavaderas 2×2 + chapa. El Excel de costos tiene todo eso. OK.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sellado adicional ($956.000)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>El kit SIPCOR ya incluye cola PUR, espuma de poliuretano, membrana líquida y Flexi Band. La línea 'Materiales de sellado adicionales' del Excel repite casi lo mismo (≈ USD 620).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="C10:G10"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C11:G11"/>
   </mergeCells>
@@ -1177,16 +1231,16 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nada (solo membrana de techo en mano de obra)</t>
+          <t>Incluida en el kit SIPCOR (membrana hidrófuga + Flexi Band + Easy Band)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Agregar</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">

--- a/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
+++ b/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -635,7 +635,12 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>263.83</v>
+        <v>180.29</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Corregido: $20.400.000 de jornales / $1.550 / 73 m². El 263,83 contaba dos veces el montaje del kit.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1077,10 +1082,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
+++ b/URBANSIP/AURA/Aura_Revision_Costo_30-09-26.xlsx
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>180.29</v>
+        <v>340</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Corregido: $20.400.000 de jornales / $1.550 / 73 m². El 263,83 contaba dos veces el montaje del kit.</t>
+          <t>Mano de obra por m² (Excel de costos): obra gris con instalaciones 204 + terminaciones 136.</t>
         </is>
       </c>
     </row>
@@ -1082,10 +1082,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C13:G13"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
